--- a/out/global_metric/excel/efficientnet.xlsx
+++ b/out/global_metric/excel/efficientnet.xlsx
@@ -502,25 +502,29 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.8690476417541504</v>
+        <v>0.6943972706794739</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8594035250226946</v>
+        <v>0.6943963976053269</v>
       </c>
       <c r="D2" t="n">
-        <v>51</v>
+        <v>205</v>
       </c>
       <c r="E2" t="n">
-        <v>9</v>
+        <v>91</v>
       </c>
       <c r="F2" t="n">
-        <v>13</v>
+        <v>89</v>
       </c>
       <c r="G2" t="n">
-        <v>95</v>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+        <v>204</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.7482647296206618</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.70397498619663</v>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>efficientnet</t>
@@ -540,25 +544,29 @@
         <v>24</v>
       </c>
       <c r="B3" t="n">
-        <v>0.875</v>
+        <v>0.7079796195030212</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8662369617173535</v>
+        <v>0.7064148881255257</v>
       </c>
       <c r="D3" t="n">
-        <v>52</v>
+        <v>187</v>
       </c>
       <c r="E3" t="n">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="F3" t="n">
-        <v>12</v>
+        <v>107</v>
       </c>
       <c r="G3" t="n">
-        <v>95</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+        <v>230</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.7707771244090857</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.7374291517600939</v>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>efficientnet</t>
@@ -578,25 +586,29 @@
         <v>47</v>
       </c>
       <c r="B4" t="n">
-        <v>0.8571428656578064</v>
+        <v>0.6977928876876831</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8466220277633325</v>
+        <v>0.697247436481233</v>
       </c>
       <c r="D4" t="n">
-        <v>50</v>
+        <v>193</v>
       </c>
       <c r="E4" t="n">
-        <v>10</v>
+        <v>76</v>
       </c>
       <c r="F4" t="n">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="G4" t="n">
-        <v>94</v>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+        <v>218</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.7990891271762942</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.8003063183733136</v>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>efficientnet</t>
@@ -616,25 +628,29 @@
         <v>70</v>
       </c>
       <c r="B5" t="n">
-        <v>0.8809523582458496</v>
+        <v>0.6910017132759094</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8758681787324347</v>
+        <v>0.6901433641652366</v>
       </c>
       <c r="D5" t="n">
-        <v>57</v>
+        <v>188</v>
       </c>
       <c r="E5" t="n">
-        <v>13</v>
+        <v>76</v>
       </c>
       <c r="F5" t="n">
-        <v>7</v>
+        <v>106</v>
       </c>
       <c r="G5" t="n">
-        <v>91</v>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+        <v>219</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.7588493024328375</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.724712166853591</v>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>efficientnet</t>
@@ -654,25 +670,29 @@
         <v>93</v>
       </c>
       <c r="B6" t="n">
-        <v>0.8452380895614624</v>
+        <v>0.7147707939147949</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8301974758683821</v>
+        <v>0.7147502371237504</v>
       </c>
       <c r="D6" t="n">
-        <v>46</v>
+        <v>208</v>
       </c>
       <c r="E6" t="n">
-        <v>8</v>
+        <v>81</v>
       </c>
       <c r="F6" t="n">
-        <v>18</v>
+        <v>87</v>
       </c>
       <c r="G6" t="n">
-        <v>96</v>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+        <v>213</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.7871786002536608</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.772586980624543</v>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>efficientnet</t>
@@ -768,25 +788,29 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>0.863095223903656</v>
+        <v>0.6808149218559265</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8588905474511712</v>
+        <v>0.6758354947155263</v>
       </c>
       <c r="D2" t="n">
+        <v>164</v>
+      </c>
+      <c r="E2" t="n">
         <v>58</v>
       </c>
-      <c r="E2" t="n">
-        <v>17</v>
-      </c>
       <c r="F2" t="n">
-        <v>6</v>
+        <v>130</v>
       </c>
       <c r="G2" t="n">
-        <v>87</v>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+        <v>237</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.761293670010377</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.7549367566577695</v>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>efficientnet</t>
@@ -806,25 +830,29 @@
         <v>25</v>
       </c>
       <c r="B3" t="n">
-        <v>0.863095223903656</v>
+        <v>0.7249575257301331</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8568835831802322</v>
+        <v>0.7249377284749912</v>
       </c>
       <c r="D3" t="n">
-        <v>55</v>
+        <v>211</v>
       </c>
       <c r="E3" t="n">
-        <v>14</v>
+        <v>79</v>
       </c>
       <c r="F3" t="n">
-        <v>9</v>
+        <v>83</v>
       </c>
       <c r="G3" t="n">
-        <v>90</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+        <v>216</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.802461662631154</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.7780139989446189</v>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>efficientnet</t>
@@ -844,25 +872,29 @@
         <v>48</v>
       </c>
       <c r="B4" t="n">
-        <v>0.8154761791229248</v>
+        <v>0.7147707939147949</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8049657290874135</v>
+        <v>0.7110316743272658</v>
       </c>
       <c r="D4" t="n">
-        <v>49</v>
+        <v>177</v>
       </c>
       <c r="E4" t="n">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="F4" t="n">
-        <v>15</v>
+        <v>118</v>
       </c>
       <c r="G4" t="n">
-        <v>88</v>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+        <v>244</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.8050616856912256</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.7930065735490013</v>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>efficientnet</t>
@@ -882,25 +914,29 @@
         <v>71</v>
       </c>
       <c r="B5" t="n">
-        <v>0.9047619104385376</v>
+        <v>0.7402377128601074</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9016249400122244</v>
+        <v>0.7369345913919841</v>
       </c>
       <c r="D5" t="n">
-        <v>61</v>
+        <v>185</v>
       </c>
       <c r="E5" t="n">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="G5" t="n">
-        <v>91</v>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+        <v>251</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.8144240747146316</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.7967002415540174</v>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>efficientnet</t>
@@ -920,25 +956,29 @@
         <v>94</v>
       </c>
       <c r="B6" t="n">
-        <v>0.8154761791229248</v>
+        <v>0.7283531427383423</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8071039617192344</v>
+        <v>0.7272769316078697</v>
       </c>
       <c r="D6" t="n">
-        <v>51</v>
+        <v>196</v>
       </c>
       <c r="E6" t="n">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="F6" t="n">
-        <v>13</v>
+        <v>99</v>
       </c>
       <c r="G6" t="n">
-        <v>86</v>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+        <v>233</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.8038510319381991</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.7994690892157608</v>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>efficientnet</t>
@@ -1034,25 +1074,29 @@
         <v>3</v>
       </c>
       <c r="B2" t="n">
-        <v>0.7857142686843872</v>
+        <v>0.6791171431541443</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7754010644265081</v>
+        <v>0.6767879957439562</v>
       </c>
       <c r="D2" t="n">
-        <v>48</v>
+        <v>175</v>
       </c>
       <c r="E2" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="F2" t="n">
-        <v>16</v>
+        <v>119</v>
       </c>
       <c r="G2" t="n">
-        <v>84</v>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+        <v>225</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.7380606479880087</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.703182448642753</v>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>efficientnet</t>
@@ -1072,25 +1116,29 @@
         <v>26</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8392857313156128</v>
+        <v>0.706281840801239</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8328358158029486</v>
+        <v>0.7050541664748338</v>
       </c>
       <c r="D3" t="n">
-        <v>54</v>
+        <v>189</v>
       </c>
       <c r="E3" t="n">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="F3" t="n">
-        <v>10</v>
+        <v>105</v>
       </c>
       <c r="G3" t="n">
-        <v>87</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+        <v>227</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.7606422229908912</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.7338015730681284</v>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>efficientnet</t>
@@ -1110,25 +1158,29 @@
         <v>49</v>
       </c>
       <c r="B4" t="n">
-        <v>0.8273809552192688</v>
+        <v>0.7028862237930298</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8164487761211657</v>
+        <v>0.6995572372869738</v>
       </c>
       <c r="D4" t="n">
-        <v>49</v>
+        <v>176</v>
       </c>
       <c r="E4" t="n">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="F4" t="n">
-        <v>15</v>
+        <v>119</v>
       </c>
       <c r="G4" t="n">
-        <v>90</v>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+        <v>238</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.776893808370806</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.748006428310483</v>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>efficientnet</t>
@@ -1148,25 +1200,29 @@
         <v>72</v>
       </c>
       <c r="B5" t="n">
-        <v>0.8571428656578064</v>
+        <v>0.6825127601623535</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8510418155023045</v>
+        <v>0.6738484723389557</v>
       </c>
       <c r="D5" t="n">
-        <v>55</v>
+        <v>153</v>
       </c>
       <c r="E5" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="F5" t="n">
-        <v>9</v>
+        <v>141</v>
       </c>
       <c r="G5" t="n">
-        <v>89</v>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+        <v>249</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.7648103309120259</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.7333806178858127</v>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>efficientnet</t>
@@ -1186,25 +1242,29 @@
         <v>95</v>
       </c>
       <c r="B6" t="n">
-        <v>0.8571428656578064</v>
+        <v>0.7113752365112305</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8476190425134795</v>
+        <v>0.7107674303987697</v>
       </c>
       <c r="D6" t="n">
-        <v>51</v>
+        <v>196</v>
       </c>
       <c r="E6" t="n">
-        <v>11</v>
+        <v>71</v>
       </c>
       <c r="F6" t="n">
-        <v>13</v>
+        <v>99</v>
       </c>
       <c r="G6" t="n">
-        <v>93</v>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+        <v>223</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.786567508359276</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.7804309914787797</v>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>efficientnet</t>
@@ -1300,25 +1360,29 @@
         <v>4</v>
       </c>
       <c r="B2" t="n">
-        <v>0.863095223903656</v>
+        <v>0.6825127601623535</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8588905474511712</v>
+        <v>0.6825090677522869</v>
       </c>
       <c r="D2" t="n">
-        <v>58</v>
+        <v>202</v>
       </c>
       <c r="E2" t="n">
-        <v>17</v>
+        <v>95</v>
       </c>
       <c r="F2" t="n">
-        <v>6</v>
+        <v>92</v>
       </c>
       <c r="G2" t="n">
-        <v>87</v>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+        <v>200</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.7349936584803413</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.7185878457066219</v>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>efficientnet</t>
@@ -1338,25 +1402,29 @@
         <v>27</v>
       </c>
       <c r="B3" t="n">
-        <v>0.886904776096344</v>
+        <v>0.7113752365112305</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8843436305742297</v>
+        <v>0.71123453724444</v>
       </c>
       <c r="D3" t="n">
-        <v>62</v>
+        <v>203</v>
       </c>
       <c r="E3" t="n">
-        <v>17</v>
+        <v>79</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>91</v>
       </c>
       <c r="G3" t="n">
-        <v>87</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+        <v>216</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.7762884814942926</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.7556864308509511</v>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>efficientnet</t>
@@ -1376,25 +1444,29 @@
         <v>50</v>
       </c>
       <c r="B4" t="n">
-        <v>0.851190447807312</v>
+        <v>0.7164685726165771</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8427142966590845</v>
+        <v>0.7159970499443662</v>
       </c>
       <c r="D4" t="n">
-        <v>52</v>
+        <v>199</v>
       </c>
       <c r="E4" t="n">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="F4" t="n">
-        <v>12</v>
+        <v>96</v>
       </c>
       <c r="G4" t="n">
-        <v>91</v>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+        <v>223</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.7879741727199354</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.7883640741891231</v>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>efficientnet</t>
@@ -1414,25 +1486,29 @@
         <v>73</v>
       </c>
       <c r="B5" t="n">
-        <v>0.8214285969734192</v>
+        <v>0.7028862237930298</v>
       </c>
       <c r="C5" t="n">
-        <v>0.818312900513247</v>
+        <v>0.701062914627071</v>
       </c>
       <c r="D5" t="n">
-        <v>58</v>
+        <v>184</v>
       </c>
       <c r="E5" t="n">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="F5" t="n">
-        <v>6</v>
+        <v>110</v>
       </c>
       <c r="G5" t="n">
-        <v>80</v>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+        <v>230</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.7804911795226566</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.7748948998641254</v>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>efficientnet</t>
@@ -1452,25 +1528,29 @@
         <v>96</v>
       </c>
       <c r="B6" t="n">
-        <v>0.875</v>
+        <v>0.706281840801239</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8726123798556147</v>
+        <v>0.7062784419822035</v>
       </c>
       <c r="D6" t="n">
-        <v>62</v>
+        <v>207</v>
       </c>
       <c r="E6" t="n">
-        <v>19</v>
+        <v>85</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>88</v>
       </c>
       <c r="G6" t="n">
-        <v>85</v>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+        <v>209</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.7782658826242361</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.7607160938518214</v>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>efficientnet</t>
@@ -1566,25 +1646,29 @@
         <v>5</v>
       </c>
       <c r="B2" t="n">
-        <v>0.8571428656578064</v>
+        <v>0.6672325730323792</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8406827829894281</v>
+        <v>0.66385976674872</v>
       </c>
       <c r="D2" t="n">
-        <v>45</v>
+        <v>167</v>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>69</v>
       </c>
       <c r="F2" t="n">
-        <v>19</v>
+        <v>127</v>
       </c>
       <c r="G2" t="n">
-        <v>99</v>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+        <v>226</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.7319381990084168</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.7122572065420557</v>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>efficientnet</t>
@@ -1604,25 +1688,29 @@
         <v>28</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8571428656578064</v>
+        <v>0.7130730152130127</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8502673745771652</v>
+        <v>0.7091969789488595</v>
       </c>
       <c r="D3" t="n">
-        <v>54</v>
+        <v>176</v>
       </c>
       <c r="E3" t="n">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="F3" t="n">
-        <v>10</v>
+        <v>118</v>
       </c>
       <c r="G3" t="n">
-        <v>90</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+        <v>244</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.7659921595756947</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.7160369602746998</v>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>efficientnet</t>
@@ -1642,25 +1730,29 @@
         <v>51</v>
       </c>
       <c r="B4" t="n">
-        <v>0.7976190447807312</v>
+        <v>0.6910017132759094</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7878787827849509</v>
+        <v>0.6844296027391783</v>
       </c>
       <c r="D4" t="n">
-        <v>49</v>
+        <v>161</v>
       </c>
       <c r="E4" t="n">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="F4" t="n">
-        <v>15</v>
+        <v>134</v>
       </c>
       <c r="G4" t="n">
-        <v>85</v>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+        <v>246</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.7674968292401707</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.7498899120470415</v>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>efficientnet</t>
@@ -1680,25 +1772,29 @@
         <v>74</v>
       </c>
       <c r="B5" t="n">
-        <v>0.8690476417541504</v>
+        <v>0.6926994919776917</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8594035250226946</v>
+        <v>0.6887919031447152</v>
       </c>
       <c r="D5" t="n">
-        <v>51</v>
+        <v>171</v>
       </c>
       <c r="E5" t="n">
-        <v>9</v>
+        <v>58</v>
       </c>
       <c r="F5" t="n">
-        <v>13</v>
+        <v>123</v>
       </c>
       <c r="G5" t="n">
-        <v>95</v>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+        <v>237</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.7735500980053038</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.749079540120826</v>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>efficientnet</t>
@@ -1718,25 +1814,29 @@
         <v>97</v>
       </c>
       <c r="B6" t="n">
-        <v>0.8452380895614624</v>
+        <v>0.6757215857505798</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8368931987803674</v>
+        <v>0.6648673559287663</v>
       </c>
       <c r="D6" t="n">
-        <v>52</v>
+        <v>146</v>
       </c>
       <c r="E6" t="n">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="F6" t="n">
-        <v>12</v>
+        <v>149</v>
       </c>
       <c r="G6" t="n">
-        <v>90</v>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+        <v>252</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.7799723279142164</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.7601817508961438</v>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>efficientnet</t>
@@ -1832,25 +1932,29 @@
         <v>6</v>
       </c>
       <c r="B2" t="n">
-        <v>0.7797619104385376</v>
+        <v>0.6876060962677002</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7784352115773598</v>
+        <v>0.6850560232864324</v>
       </c>
       <c r="D2" t="n">
-        <v>59</v>
+        <v>176</v>
       </c>
       <c r="E2" t="n">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="F2" t="n">
-        <v>5</v>
+        <v>118</v>
       </c>
       <c r="G2" t="n">
-        <v>72</v>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+        <v>229</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.7547215496368038</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.7094150525428967</v>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>efficientnet</t>
@@ -1870,25 +1974,29 @@
         <v>29</v>
       </c>
       <c r="B3" t="n">
-        <v>0.738095223903656</v>
+        <v>0.7079796195030212</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7380581100369508</v>
+        <v>0.7075336562684413</v>
       </c>
       <c r="D3" t="n">
-        <v>63</v>
+        <v>197</v>
       </c>
       <c r="E3" t="n">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>97</v>
       </c>
       <c r="G3" t="n">
-        <v>61</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+        <v>220</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.7754006687420731</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.7434636356496251</v>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>efficientnet</t>
@@ -1908,25 +2016,29 @@
         <v>52</v>
       </c>
       <c r="B4" t="n">
-        <v>0.7440476417541504</v>
+        <v>0.7215619683265686</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7439659706990933</v>
+        <v>0.7209756385603663</v>
       </c>
       <c r="D4" t="n">
-        <v>61</v>
+        <v>199</v>
       </c>
       <c r="E4" t="n">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>96</v>
       </c>
       <c r="G4" t="n">
-        <v>64</v>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+        <v>226</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.7840539605672777</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.7351184215082711</v>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>efficientnet</t>
@@ -1946,25 +2058,29 @@
         <v>75</v>
       </c>
       <c r="B5" t="n">
-        <v>0.7559523582458496</v>
+        <v>0.7164685726165771</v>
       </c>
       <c r="C5" t="n">
-        <v>0.755874529974655</v>
+        <v>0.7130810130469891</v>
       </c>
       <c r="D5" t="n">
-        <v>62</v>
+        <v>179</v>
       </c>
       <c r="E5" t="n">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>115</v>
       </c>
       <c r="G5" t="n">
-        <v>65</v>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+        <v>243</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.7953649256312695</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.7706439528873752</v>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>efficientnet</t>
@@ -1984,25 +2100,29 @@
         <v>98</v>
       </c>
       <c r="B6" t="n">
-        <v>0.7083333134651184</v>
+        <v>0.7011884450912476</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7080747496992692</v>
+        <v>0.6987492394512703</v>
       </c>
       <c r="D6" t="n">
-        <v>62</v>
+        <v>180</v>
       </c>
       <c r="E6" t="n">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>115</v>
       </c>
       <c r="G6" t="n">
-        <v>57</v>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+        <v>233</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.766389945808832</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.7419895234451508</v>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>efficientnet</t>
@@ -2098,25 +2218,29 @@
         <v>7</v>
       </c>
       <c r="B2" t="n">
-        <v>0.8214285969734192</v>
+        <v>0.6740237474441528</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8193548337000052</v>
+        <v>0.6732316177346791</v>
       </c>
       <c r="D2" t="n">
-        <v>60</v>
+        <v>184</v>
       </c>
       <c r="E2" t="n">
-        <v>26</v>
+        <v>82</v>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>110</v>
       </c>
       <c r="G2" t="n">
-        <v>78</v>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+        <v>213</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.7538337368845844</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.7291221053462377</v>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>efficientnet</t>
@@ -2136,25 +2260,29 @@
         <v>30</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8095238208770752</v>
+        <v>0.7045840620994568</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8077803153741576</v>
+        <v>0.7017912378354427</v>
       </c>
       <c r="D3" t="n">
-        <v>60</v>
+        <v>179</v>
       </c>
       <c r="E3" t="n">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="F3" t="n">
-        <v>4</v>
+        <v>115</v>
       </c>
       <c r="G3" t="n">
-        <v>76</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+        <v>236</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.7858584111610746</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.7805575798141285</v>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>efficientnet</t>
@@ -2174,25 +2302,29 @@
         <v>53</v>
       </c>
       <c r="B4" t="n">
-        <v>0.7797619104385376</v>
+        <v>0.6926994919776917</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7793788770886074</v>
+        <v>0.6906449718991488</v>
       </c>
       <c r="D4" t="n">
-        <v>62</v>
+        <v>180</v>
       </c>
       <c r="E4" t="n">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>115</v>
       </c>
       <c r="G4" t="n">
-        <v>69</v>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+        <v>228</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.7776893808370806</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.7686212102679975</v>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>efficientnet</t>
@@ -2212,25 +2344,29 @@
         <v>76</v>
       </c>
       <c r="B5" t="n">
-        <v>0.8392857313156128</v>
+        <v>0.6960950493812561</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8362159184049769</v>
+        <v>0.6960074455067666</v>
       </c>
       <c r="D5" t="n">
-        <v>59</v>
+        <v>200</v>
       </c>
       <c r="E5" t="n">
-        <v>22</v>
+        <v>85</v>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>94</v>
       </c>
       <c r="G5" t="n">
-        <v>82</v>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+        <v>210</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.7700564971751412</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.7466910102278357</v>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>efficientnet</t>
@@ -2250,25 +2386,29 @@
         <v>99</v>
       </c>
       <c r="B6" t="n">
-        <v>0.7559523582458496</v>
+        <v>0.6791171431541443</v>
       </c>
       <c r="C6" t="n">
-        <v>0.755874529974655</v>
+        <v>0.6784906591126197</v>
       </c>
       <c r="D6" t="n">
-        <v>62</v>
+        <v>187</v>
       </c>
       <c r="E6" t="n">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>108</v>
       </c>
       <c r="G6" t="n">
-        <v>65</v>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+        <v>213</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.7714285714285715</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.7597467018061745</v>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>efficientnet</t>
@@ -2364,25 +2504,29 @@
         <v>8</v>
       </c>
       <c r="B2" t="n">
-        <v>0.8928571343421936</v>
+        <v>0.7096773982048035</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8897959132865056</v>
+        <v>0.7090198339519671</v>
       </c>
       <c r="D2" t="n">
-        <v>61</v>
+        <v>195</v>
       </c>
       <c r="E2" t="n">
-        <v>15</v>
+        <v>72</v>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>99</v>
       </c>
       <c r="G2" t="n">
-        <v>89</v>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+        <v>223</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.7737230485414506</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.756824473247439</v>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>efficientnet</t>
@@ -2402,25 +2546,29 @@
         <v>31</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8273809552192688</v>
+        <v>0.6943972706794739</v>
       </c>
       <c r="C3" t="n">
-        <v>0.825144451788471</v>
+        <v>0.6943893502021845</v>
       </c>
       <c r="D3" t="n">
-        <v>60</v>
+        <v>206</v>
       </c>
       <c r="E3" t="n">
-        <v>25</v>
+        <v>92</v>
       </c>
       <c r="F3" t="n">
-        <v>4</v>
+        <v>88</v>
       </c>
       <c r="G3" t="n">
-        <v>79</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+        <v>203</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.7657615588608324</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.7457807028926434</v>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>efficientnet</t>
@@ -2440,25 +2588,29 @@
         <v>54</v>
       </c>
       <c r="B4" t="n">
-        <v>0.8154761791229248</v>
+        <v>0.7266553640365601</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8105837374325401</v>
+        <v>0.726453487544364</v>
       </c>
       <c r="D4" t="n">
-        <v>55</v>
+        <v>206</v>
       </c>
       <c r="E4" t="n">
-        <v>22</v>
+        <v>72</v>
       </c>
       <c r="F4" t="n">
-        <v>9</v>
+        <v>89</v>
       </c>
       <c r="G4" t="n">
-        <v>82</v>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+        <v>222</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.7996310388562204</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.786438177755274</v>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>efficientnet</t>
@@ -2478,25 +2630,29 @@
         <v>77</v>
       </c>
       <c r="B5" t="n">
-        <v>0.8571428656578064</v>
+        <v>0.7283531427383423</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8536372825770167</v>
+        <v>0.7282207406399497</v>
       </c>
       <c r="D5" t="n">
-        <v>59</v>
+        <v>208</v>
       </c>
       <c r="E5" t="n">
-        <v>19</v>
+        <v>74</v>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>86</v>
       </c>
       <c r="G5" t="n">
-        <v>85</v>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+        <v>221</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.7855874553211114</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.7553025089593821</v>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>efficientnet</t>
@@ -2516,25 +2672,29 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>0.8095238208770752</v>
+        <v>0.706281840801239</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8055555505063658</v>
+        <v>0.7057083806672377</v>
       </c>
       <c r="D6" t="n">
-        <v>56</v>
+        <v>195</v>
       </c>
       <c r="E6" t="n">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="F6" t="n">
-        <v>8</v>
+        <v>100</v>
       </c>
       <c r="G6" t="n">
-        <v>80</v>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+        <v>221</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.7964718090626081</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.7952650150199776</v>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>efficientnet</t>

--- a/out/global_metric/excel/efficientnet.xlsx
+++ b/out/global_metric/excel/efficientnet.xlsx
@@ -502,28 +502,28 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.6943972706794739</v>
+        <v>0.7079796195030212</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6943963976053269</v>
+        <v>0.7071684537703899</v>
       </c>
       <c r="D2" t="n">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="E2" t="n">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="F2" t="n">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="G2" t="n">
-        <v>204</v>
+        <v>224</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7482647296206618</v>
+        <v>0.7721434336446443</v>
       </c>
       <c r="I2" t="n">
-        <v>0.70397498619663</v>
+        <v>0.7419836413840303</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -544,28 +544,28 @@
         <v>24</v>
       </c>
       <c r="B3" t="n">
-        <v>0.7079796195030212</v>
+        <v>0.7266553640365601</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7064148881255257</v>
+        <v>0.7249778810565503</v>
       </c>
       <c r="D3" t="n">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="E3" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="F3" t="n">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="G3" t="n">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7707771244090857</v>
+        <v>0.788913870632999</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7374291517600939</v>
+        <v>0.7645479717110897</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -586,28 +586,28 @@
         <v>47</v>
       </c>
       <c r="B4" t="n">
-        <v>0.6977928876876831</v>
+        <v>0.7266553640365601</v>
       </c>
       <c r="C4" t="n">
-        <v>0.697247436481233</v>
+        <v>0.7265008241659671</v>
       </c>
       <c r="D4" t="n">
-        <v>193</v>
+        <v>221</v>
       </c>
       <c r="E4" t="n">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="F4" t="n">
-        <v>102</v>
+        <v>73</v>
       </c>
       <c r="G4" t="n">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7990891271762942</v>
+        <v>0.8184941773319497</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8003063183733136</v>
+        <v>0.8064350079554992</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -628,28 +628,28 @@
         <v>70</v>
       </c>
       <c r="B5" t="n">
-        <v>0.6910017132759094</v>
+        <v>0.7130730152130127</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6901433641652366</v>
+        <v>0.7116065972157282</v>
       </c>
       <c r="D5" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E5" t="n">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="F5" t="n">
         <v>106</v>
       </c>
       <c r="G5" t="n">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7588493024328375</v>
+        <v>0.8015219647180907</v>
       </c>
       <c r="I5" t="n">
-        <v>0.724712166853591</v>
+        <v>0.7862422882290152</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -670,28 +670,28 @@
         <v>93</v>
       </c>
       <c r="B6" t="n">
-        <v>0.7147707939147949</v>
+        <v>0.7198641896247864</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7147502371237504</v>
+        <v>0.7163020107185344</v>
       </c>
       <c r="D6" t="n">
-        <v>208</v>
+        <v>179</v>
       </c>
       <c r="E6" t="n">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="F6" t="n">
-        <v>87</v>
+        <v>116</v>
       </c>
       <c r="G6" t="n">
-        <v>213</v>
+        <v>245</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7871786002536608</v>
+        <v>0.8013028940389715</v>
       </c>
       <c r="I6" t="n">
-        <v>0.772586980624543</v>
+        <v>0.7839722044096593</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -788,28 +788,28 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>0.6808149218559265</v>
+        <v>0.706281840801239</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6758354947155263</v>
+        <v>0.7046335297944624</v>
       </c>
       <c r="D2" t="n">
-        <v>164</v>
+        <v>186</v>
       </c>
       <c r="E2" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="F2" t="n">
-        <v>130</v>
+        <v>108</v>
       </c>
       <c r="G2" t="n">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="H2" t="n">
-        <v>0.761293670010377</v>
+        <v>0.784180790960452</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7549367566577695</v>
+        <v>0.7719096321748731</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -830,28 +830,28 @@
         <v>25</v>
       </c>
       <c r="B3" t="n">
-        <v>0.7249575257301331</v>
+        <v>0.7300509214401245</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7249377284749912</v>
+        <v>0.7298983293925289</v>
       </c>
       <c r="D3" t="n">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="E3" t="n">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="F3" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="G3" t="n">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="H3" t="n">
-        <v>0.802461662631154</v>
+        <v>0.8094258042199931</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7780139989446189</v>
+        <v>0.7878085828231158</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -872,28 +872,28 @@
         <v>48</v>
       </c>
       <c r="B4" t="n">
-        <v>0.7147707939147949</v>
+        <v>0.7538200616836548</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7110316743272658</v>
+        <v>0.7537944801787932</v>
       </c>
       <c r="D4" t="n">
-        <v>177</v>
+        <v>219</v>
       </c>
       <c r="E4" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="F4" t="n">
-        <v>118</v>
+        <v>75</v>
       </c>
       <c r="G4" t="n">
-        <v>244</v>
+        <v>225</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8050616856912256</v>
+        <v>0.8256889196356508</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7930065735490013</v>
+        <v>0.8018543676941282</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -914,28 +914,28 @@
         <v>71</v>
       </c>
       <c r="B5" t="n">
-        <v>0.7402377128601074</v>
+        <v>0.7317487001419067</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7369345913919841</v>
+        <v>0.7317293893760104</v>
       </c>
       <c r="D5" t="n">
-        <v>185</v>
+        <v>218</v>
       </c>
       <c r="E5" t="n">
-        <v>44</v>
+        <v>81</v>
       </c>
       <c r="F5" t="n">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="G5" t="n">
-        <v>251</v>
+        <v>213</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8144240747146316</v>
+        <v>0.8019831661478151</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7967002415540174</v>
+        <v>0.7990899471031904</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -956,28 +956,28 @@
         <v>94</v>
       </c>
       <c r="B6" t="n">
-        <v>0.7283531427383423</v>
+        <v>0.7538200616836548</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7272769316078697</v>
+        <v>0.7537178020978414</v>
       </c>
       <c r="D6" t="n">
-        <v>196</v>
+        <v>216</v>
       </c>
       <c r="E6" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="F6" t="n">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="G6" t="n">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8038510319381991</v>
+        <v>0.8321226795803067</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7994690892157608</v>
+        <v>0.8327661213034746</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1074,28 +1074,28 @@
         <v>3</v>
       </c>
       <c r="B2" t="n">
-        <v>0.6791171431541443</v>
+        <v>0.7147707939147949</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6767879957439562</v>
+        <v>0.7122618416236177</v>
       </c>
       <c r="D2" t="n">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="E2" t="n">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="F2" t="n">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="G2" t="n">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7380606479880087</v>
+        <v>0.7681079211345557</v>
       </c>
       <c r="I2" t="n">
-        <v>0.703182448642753</v>
+        <v>0.7304448104521635</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -1116,28 +1116,28 @@
         <v>26</v>
       </c>
       <c r="B3" t="n">
-        <v>0.706281840801239</v>
+        <v>0.7028862237930298</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7050541664748338</v>
+        <v>0.6986296113577892</v>
       </c>
       <c r="D3" t="n">
-        <v>189</v>
+        <v>172</v>
       </c>
       <c r="E3" t="n">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="F3" t="n">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="G3" t="n">
-        <v>227</v>
+        <v>242</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7606422229908912</v>
+        <v>0.7796321918597948</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7338015730681284</v>
+        <v>0.7600962215706495</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -1158,28 +1158,28 @@
         <v>49</v>
       </c>
       <c r="B4" t="n">
-        <v>0.7028862237930298</v>
+        <v>0.7368420958518982</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6995572372869738</v>
+        <v>0.7359622815148936</v>
       </c>
       <c r="D4" t="n">
-        <v>176</v>
+        <v>200</v>
       </c>
       <c r="E4" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="F4" t="n">
-        <v>119</v>
+        <v>94</v>
       </c>
       <c r="G4" t="n">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="H4" t="n">
-        <v>0.776893808370806</v>
+        <v>0.8181943964026288</v>
       </c>
       <c r="I4" t="n">
-        <v>0.748006428310483</v>
+        <v>0.8012641713235501</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -1200,28 +1200,28 @@
         <v>72</v>
       </c>
       <c r="B5" t="n">
-        <v>0.6825127601623535</v>
+        <v>0.685908317565918</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6738484723389557</v>
+        <v>0.6856763684249856</v>
       </c>
       <c r="D5" t="n">
-        <v>153</v>
+        <v>194</v>
       </c>
       <c r="E5" t="n">
-        <v>46</v>
+        <v>84</v>
       </c>
       <c r="F5" t="n">
-        <v>141</v>
+        <v>101</v>
       </c>
       <c r="G5" t="n">
-        <v>249</v>
+        <v>210</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7648103309120259</v>
+        <v>0.75993312579269</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7333806178858127</v>
+        <v>0.7368705739455371</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -1242,28 +1242,28 @@
         <v>95</v>
       </c>
       <c r="B6" t="n">
-        <v>0.7113752365112305</v>
+        <v>0.7385398745536804</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7107674303987697</v>
+        <v>0.7376133894212481</v>
       </c>
       <c r="D6" t="n">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="E6" t="n">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="F6" t="n">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="G6" t="n">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="H6" t="n">
-        <v>0.786567508359276</v>
+        <v>0.8116107459933126</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7804309914787797</v>
+        <v>0.8022119625785632</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1360,28 +1360,28 @@
         <v>4</v>
       </c>
       <c r="B2" t="n">
-        <v>0.6825127601623535</v>
+        <v>0.6689304113388062</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6825090677522869</v>
+        <v>0.665688658042114</v>
       </c>
       <c r="D2" t="n">
-        <v>202</v>
+        <v>168</v>
       </c>
       <c r="E2" t="n">
-        <v>95</v>
+        <v>69</v>
       </c>
       <c r="F2" t="n">
-        <v>92</v>
+        <v>126</v>
       </c>
       <c r="G2" t="n">
-        <v>200</v>
+        <v>226</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7349936584803413</v>
+        <v>0.7606941081517352</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7185878457066219</v>
+        <v>0.7631379864116004</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -1402,28 +1402,28 @@
         <v>27</v>
       </c>
       <c r="B3" t="n">
-        <v>0.7113752365112305</v>
+        <v>0.7147707939147949</v>
       </c>
       <c r="C3" t="n">
-        <v>0.71123453724444</v>
+        <v>0.7144077530050613</v>
       </c>
       <c r="D3" t="n">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E3" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="F3" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="G3" t="n">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7762884814942926</v>
+        <v>0.7861005419116799</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7556864308509511</v>
+        <v>0.761646546837016</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -1444,28 +1444,28 @@
         <v>50</v>
       </c>
       <c r="B4" t="n">
-        <v>0.7164685726165771</v>
+        <v>0.7538200616836548</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7159970499443662</v>
+        <v>0.7526793860559229</v>
       </c>
       <c r="D4" t="n">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="E4" t="n">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="F4" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="G4" t="n">
-        <v>223</v>
+        <v>242</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7879741727199354</v>
+        <v>0.8177677850801337</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7883640741891231</v>
+        <v>0.7731206882504892</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -1486,28 +1486,28 @@
         <v>73</v>
       </c>
       <c r="B5" t="n">
-        <v>0.7028862237930298</v>
+        <v>0.7079796195030212</v>
       </c>
       <c r="C5" t="n">
-        <v>0.701062914627071</v>
+        <v>0.7057736939005467</v>
       </c>
       <c r="D5" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E5" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="F5" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G5" t="n">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7804911795226566</v>
+        <v>0.7959414274184249</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7748948998641254</v>
+        <v>0.7851870244117956</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -1528,28 +1528,28 @@
         <v>96</v>
       </c>
       <c r="B6" t="n">
-        <v>0.706281840801239</v>
+        <v>0.7028862237930298</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7062784419822035</v>
+        <v>0.6991081934873669</v>
       </c>
       <c r="D6" t="n">
-        <v>207</v>
+        <v>174</v>
       </c>
       <c r="E6" t="n">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="F6" t="n">
-        <v>88</v>
+        <v>121</v>
       </c>
       <c r="G6" t="n">
-        <v>209</v>
+        <v>240</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7782658826242361</v>
+        <v>0.783558169030324</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7607160938518214</v>
+        <v>0.7750567056613373</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1646,28 +1646,28 @@
         <v>5</v>
       </c>
       <c r="B2" t="n">
-        <v>0.6672325730323792</v>
+        <v>0.6740237474441528</v>
       </c>
       <c r="C2" t="n">
-        <v>0.66385976674872</v>
+        <v>0.6721098484105898</v>
       </c>
       <c r="D2" t="n">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="E2" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="F2" t="n">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="G2" t="n">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7319381990084168</v>
+        <v>0.744644298397325</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7122572065420557</v>
+        <v>0.7142157795518247</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -1691,25 +1691,25 @@
         <v>0.7130730152130127</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7091969789488595</v>
+        <v>0.7117435611292156</v>
       </c>
       <c r="D3" t="n">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="E3" t="n">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="F3" t="n">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="G3" t="n">
-        <v>244</v>
+        <v>230</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7659921595756947</v>
+        <v>0.7804047042545832</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7160369602746998</v>
+        <v>0.7349245054983117</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -1730,28 +1730,28 @@
         <v>51</v>
       </c>
       <c r="B4" t="n">
-        <v>0.6910017132759094</v>
+        <v>0.7487266659736633</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6844296027391783</v>
+        <v>0.7486679686809523</v>
       </c>
       <c r="D4" t="n">
-        <v>161</v>
+        <v>216</v>
       </c>
       <c r="E4" t="n">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="F4" t="n">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="G4" t="n">
-        <v>246</v>
+        <v>225</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7674968292401707</v>
+        <v>0.8051423959414274</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7498899120470415</v>
+        <v>0.7661256144895827</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -1772,28 +1772,28 @@
         <v>74</v>
       </c>
       <c r="B5" t="n">
-        <v>0.6926994919776917</v>
+        <v>0.6876060962677002</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6887919031447152</v>
+        <v>0.68712902798806</v>
       </c>
       <c r="D5" t="n">
-        <v>171</v>
+        <v>191</v>
       </c>
       <c r="E5" t="n">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="F5" t="n">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="G5" t="n">
-        <v>237</v>
+        <v>214</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7735500980053038</v>
+        <v>0.7617202813328721</v>
       </c>
       <c r="I5" t="n">
-        <v>0.749079540120826</v>
+        <v>0.7429979669321003</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -1814,28 +1814,28 @@
         <v>97</v>
       </c>
       <c r="B6" t="n">
-        <v>0.6757215857505798</v>
+        <v>0.6893039345741272</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6648673559287663</v>
+        <v>0.6870486941360194</v>
       </c>
       <c r="D6" t="n">
-        <v>146</v>
+        <v>178</v>
       </c>
       <c r="E6" t="n">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="F6" t="n">
-        <v>149</v>
+        <v>117</v>
       </c>
       <c r="G6" t="n">
-        <v>252</v>
+        <v>228</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7799723279142164</v>
+        <v>0.7807448403090049</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7601817508961438</v>
+        <v>0.7668022524438993</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1932,28 +1932,28 @@
         <v>6</v>
       </c>
       <c r="B2" t="n">
-        <v>0.6876060962677002</v>
+        <v>0.6893039345741272</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6850560232864324</v>
+        <v>0.6822101685424875</v>
       </c>
       <c r="D2" t="n">
-        <v>176</v>
+        <v>159</v>
       </c>
       <c r="E2" t="n">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="F2" t="n">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="G2" t="n">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7547215496368038</v>
+        <v>0.7427649025711979</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7094150525428967</v>
+        <v>0.7112443571583629</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -1974,28 +1974,28 @@
         <v>29</v>
       </c>
       <c r="B3" t="n">
-        <v>0.7079796195030212</v>
+        <v>0.6994906663894653</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7075336562684413</v>
+        <v>0.6923065522483048</v>
       </c>
       <c r="D3" t="n">
-        <v>197</v>
+        <v>161</v>
       </c>
       <c r="E3" t="n">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="F3" t="n">
-        <v>97</v>
+        <v>133</v>
       </c>
       <c r="G3" t="n">
-        <v>220</v>
+        <v>251</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7754006687420731</v>
+        <v>0.7887755102040817</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7434636356496251</v>
+        <v>0.7781920651645877</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -2016,28 +2016,28 @@
         <v>52</v>
       </c>
       <c r="B4" t="n">
-        <v>0.7215619683265686</v>
+        <v>0.7130730152130127</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7209756385603663</v>
+        <v>0.7098581318342898</v>
       </c>
       <c r="D4" t="n">
-        <v>199</v>
+        <v>179</v>
       </c>
       <c r="E4" t="n">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="F4" t="n">
-        <v>96</v>
+        <v>115</v>
       </c>
       <c r="G4" t="n">
-        <v>226</v>
+        <v>241</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7840539605672777</v>
+        <v>0.79844344517468</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7351184215082711</v>
+        <v>0.7697519440913175</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -2058,28 +2058,28 @@
         <v>75</v>
       </c>
       <c r="B5" t="n">
-        <v>0.7164685726165771</v>
+        <v>0.7096773982048035</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7130810130469891</v>
+        <v>0.7068346687497791</v>
       </c>
       <c r="D5" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E5" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F5" t="n">
         <v>115</v>
       </c>
       <c r="G5" t="n">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7953649256312695</v>
+        <v>0.7848380029978093</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7706439528873752</v>
+        <v>0.7663414856269171</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -2100,28 +2100,28 @@
         <v>98</v>
       </c>
       <c r="B6" t="n">
-        <v>0.7011884450912476</v>
+        <v>0.7164685726165771</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6987492394512703</v>
+        <v>0.7126384347645858</v>
       </c>
       <c r="D6" t="n">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E6" t="n">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="F6" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="G6" t="n">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="H6" t="n">
-        <v>0.766389945808832</v>
+        <v>0.8052461662631154</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7419895234451508</v>
+        <v>0.787400505651881</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -2218,28 +2218,28 @@
         <v>7</v>
       </c>
       <c r="B2" t="n">
-        <v>0.6740237474441528</v>
+        <v>0.6960950493812561</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6732316177346791</v>
+        <v>0.6906703154834896</v>
       </c>
       <c r="D2" t="n">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="E2" t="n">
-        <v>82</v>
+        <v>51</v>
       </c>
       <c r="F2" t="n">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="G2" t="n">
-        <v>213</v>
+        <v>244</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7538337368845844</v>
+        <v>0.7712325608209385</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7291221053462377</v>
+        <v>0.754792219066455</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -2260,28 +2260,28 @@
         <v>30</v>
       </c>
       <c r="B3" t="n">
-        <v>0.7045840620994568</v>
+        <v>0.6876060962677002</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7017912378354427</v>
+        <v>0.6824574513437716</v>
       </c>
       <c r="D3" t="n">
-        <v>179</v>
+        <v>165</v>
       </c>
       <c r="E3" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F3" t="n">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="G3" t="n">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7858584111610746</v>
+        <v>0.762902109996541</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7805575798141285</v>
+        <v>0.7568009304559355</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -2302,28 +2302,28 @@
         <v>53</v>
       </c>
       <c r="B4" t="n">
-        <v>0.6926994919776917</v>
+        <v>0.7164685726165771</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6906449718991488</v>
+        <v>0.7134955283620725</v>
       </c>
       <c r="D4" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E4" t="n">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="F4" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G4" t="n">
-        <v>228</v>
+        <v>241</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7776893808370806</v>
+        <v>0.78428456128214</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7686212102679975</v>
+        <v>0.7516337482455704</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -2344,28 +2344,28 @@
         <v>76</v>
       </c>
       <c r="B5" t="n">
-        <v>0.6960950493812561</v>
+        <v>0.6910017132759094</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6960074455067666</v>
+        <v>0.68902155503729</v>
       </c>
       <c r="D5" t="n">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="E5" t="n">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="F5" t="n">
-        <v>94</v>
+        <v>115</v>
       </c>
       <c r="G5" t="n">
-        <v>210</v>
+        <v>227</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7700564971751412</v>
+        <v>0.7692493946731236</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7466910102278357</v>
+        <v>0.7501536221839484</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -2386,28 +2386,28 @@
         <v>99</v>
       </c>
       <c r="B6" t="n">
-        <v>0.6791171431541443</v>
+        <v>0.7028862237930298</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6784906591126197</v>
+        <v>0.700899834543413</v>
       </c>
       <c r="D6" t="n">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="E6" t="n">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="F6" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="G6" t="n">
-        <v>213</v>
+        <v>231</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7714285714285715</v>
+        <v>0.7876282716476422</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7597467018061745</v>
+        <v>0.7850109970630237</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -2504,28 +2504,28 @@
         <v>8</v>
       </c>
       <c r="B2" t="n">
-        <v>0.7096773982048035</v>
+        <v>0.7147707939147949</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7090198339519671</v>
+        <v>0.7116783167075851</v>
       </c>
       <c r="D2" t="n">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="E2" t="n">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="F2" t="n">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="G2" t="n">
-        <v>223</v>
+        <v>241</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7737230485414506</v>
+        <v>0.7866366885737346</v>
       </c>
       <c r="I2" t="n">
-        <v>0.756824473247439</v>
+        <v>0.7700234512898405</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -2546,28 +2546,28 @@
         <v>31</v>
       </c>
       <c r="B3" t="n">
-        <v>0.6943972706794739</v>
+        <v>0.7011884450912476</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6943893502021845</v>
+        <v>0.7001295886244154</v>
       </c>
       <c r="D3" t="n">
-        <v>206</v>
+        <v>189</v>
       </c>
       <c r="E3" t="n">
-        <v>92</v>
+        <v>71</v>
       </c>
       <c r="F3" t="n">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="G3" t="n">
-        <v>203</v>
+        <v>224</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7657615588608324</v>
+        <v>0.7598351204888735</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7457807028926434</v>
+        <v>0.7347125227762989</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -2588,28 +2588,28 @@
         <v>54</v>
       </c>
       <c r="B4" t="n">
-        <v>0.7266553640365601</v>
+        <v>0.7402377128601074</v>
       </c>
       <c r="C4" t="n">
-        <v>0.726453487544364</v>
+        <v>0.7383521860786617</v>
       </c>
       <c r="D4" t="n">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="E4" t="n">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="F4" t="n">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="G4" t="n">
-        <v>222</v>
+        <v>243</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7996310388562204</v>
+        <v>0.8223221491986625</v>
       </c>
       <c r="I4" t="n">
-        <v>0.786438177755274</v>
+        <v>0.7981802241697383</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -2630,28 +2630,28 @@
         <v>77</v>
       </c>
       <c r="B5" t="n">
-        <v>0.7283531427383423</v>
+        <v>0.7215619683265686</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7282207406399497</v>
+        <v>0.7204588550233921</v>
       </c>
       <c r="D5" t="n">
-        <v>208</v>
+        <v>194</v>
       </c>
       <c r="E5" t="n">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="F5" t="n">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="G5" t="n">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7855874553211114</v>
+        <v>0.7832237979937737</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7553025089593821</v>
+        <v>0.7701698957933605</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -2672,28 +2672,28 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>0.706281840801239</v>
+        <v>0.7164685726165771</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7057083806672377</v>
+        <v>0.7144105565069996</v>
       </c>
       <c r="D6" t="n">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="E6" t="n">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="F6" t="n">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="G6" t="n">
-        <v>221</v>
+        <v>236</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7964718090626081</v>
+        <v>0.8018909258618701</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7952650150199776</v>
+        <v>0.8122604548577937</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
